--- a/registration_forms/030_global_conversation_registration--registration_forms.xlsx
+++ b/registration_forms/030_global_conversation_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>australia_central</t>
+          <t>europe_central</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia Central</t>
+          <t>Europe Central</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>europe_central</t>
+          <t>europe_eastern</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe Central</t>
+          <t>Europe Eastern</t>
         </is>
       </c>
     </row>
@@ -927,29 +927,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>europe_eastern</t>
+          <t>india</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe Eastern</t>
+          <t>India</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time_zone_choices</t>
+          <t>languages_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mandarin</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mandarin</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1046,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>japanese</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Japanese</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>languages_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>arabic</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Arabic</t>
         </is>
